--- a/data/trans_bre/IP04F-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Provincia-trans_bre.xlsx
@@ -563,7 +563,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -601,29 +601,29 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 14,77</t>
+          <t>-5,11; 16,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 10,87</t>
+          <t>-7,56; 11,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-37,27; 207,1</t>
+          <t>-36,82; 271,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-53,55; 130,68</t>
+          <t>-45,05; 131,1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -661,29 +661,29 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 8,18</t>
+          <t>-3,47; 7,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 5,28</t>
+          <t>-3,09; 5,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 266,85</t>
+          <t>-49,14; 237,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,66; 428,35</t>
+          <t>-69,53; 491,4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 11,76</t>
+          <t>-6,36; 10,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 3,84</t>
+          <t>-10,05; 5,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,52; 193,86</t>
+          <t>-48,07; 171,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-83,74; 111,36</t>
+          <t>-80,39; 154,86</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 10,36</t>
+          <t>-1,22; 11,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 9,22</t>
+          <t>-2,3; 9,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,81; 1285,47</t>
+          <t>-60,74; 1451,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,09; 768,89</t>
+          <t>-58,97; 741,1</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 9,33</t>
+          <t>-12,76; 9,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 10,81</t>
+          <t>-7,61; 9,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-72,46; 179,05</t>
+          <t>-71,79; 188,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-75,26; 389,31</t>
+          <t>-72,71; 407,92</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -901,29 +901,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 12,7</t>
+          <t>-5,56; 13,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 19,18</t>
+          <t>-0,02; 19,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,32; 295,92</t>
+          <t>-52,38; 312,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 602,71</t>
+          <t>-16,0; 675,37</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 6,3</t>
+          <t>-5,41; 6,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 8,29</t>
+          <t>-4,56; 8,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-49,06; 86,26</t>
+          <t>-43,89; 107,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 125,03</t>
+          <t>-36,84; 115,46</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 4,53</t>
+          <t>-7,2; 4,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 3,76</t>
+          <t>-5,79; 3,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,94; 48,68</t>
+          <t>-45,42; 52,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,11; 51,01</t>
+          <t>-50,13; 57,45</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 3,97</t>
+          <t>-1,18; 3,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,64</t>
+          <t>-1,23; 3,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 52,9</t>
+          <t>-11,65; 49,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 54,23</t>
+          <t>-15,12; 51,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04F-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Provincia-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 16,44</t>
+          <t>-5,17; 15,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 11,25</t>
+          <t>-8,4; 10,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 271,7</t>
+          <t>-37,02; 242,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-45,05; 131,1</t>
+          <t>-51,14; 130,21</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 7,04</t>
+          <t>-3,55; 7,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 5,4</t>
+          <t>-3,2; 5,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,14; 237,56</t>
+          <t>-50,09; 215,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,53; 491,4</t>
+          <t>-69,39; 475,02</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 10,88</t>
+          <t>-7,03; 10,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 5,22</t>
+          <t>-10,12; 4,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-48,07; 171,27</t>
+          <t>-47,64; 180,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-80,39; 154,86</t>
+          <t>-82,31; 119,21</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 11,37</t>
+          <t>-0,49; 10,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 9,09</t>
+          <t>-2,02; 9,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,74; 1451,96</t>
+          <t>-47,53; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,97; 741,1</t>
+          <t>-47,68; 742,79</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 9,78</t>
+          <t>-11,76; 9,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 9,79</t>
+          <t>-7,51; 10,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-71,79; 188,4</t>
+          <t>-74,7; 191,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-72,71; 407,92</t>
+          <t>-76,07; 448,25</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 13,78</t>
+          <t>-4,24; 12,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 19,7</t>
+          <t>-0,3; 18,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 312,1</t>
+          <t>-43,39; 372,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 675,37</t>
+          <t>-15,31; 654,87</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 6,92</t>
+          <t>-5,5; 6,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 8,38</t>
+          <t>-5,04; 7,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-43,89; 107,67</t>
+          <t>-44,3; 103,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-36,84; 115,46</t>
+          <t>-38,08; 107,83</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 4,81</t>
+          <t>-6,88; 5,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 3,66</t>
+          <t>-6,15; 3,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,42; 52,12</t>
+          <t>-45,7; 58,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,13; 57,45</t>
+          <t>-51,86; 59,27</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,94</t>
+          <t>-1,0; 4,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,48</t>
+          <t>-1,13; 3,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 49,63</t>
+          <t>-9,96; 52,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 51,07</t>
+          <t>-13,71; 50,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04F-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04F-Provincia-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 15,74</t>
+          <t>-5,55; 14,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 10,13</t>
+          <t>-8,79; 10,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-37,02; 242,41</t>
+          <t>-37,27; 207,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-51,14; 130,21</t>
+          <t>-53,55; 130,68</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 7,03</t>
+          <t>-3,18; 8,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,52</t>
+          <t>-3,14; 5,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 215,22</t>
+          <t>-46,33; 266,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,39; 475,02</t>
+          <t>-67,66; 428,35</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 10,88</t>
+          <t>-5,94; 11,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 4,72</t>
+          <t>-10,72; 3,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-47,64; 180,1</t>
+          <t>-43,52; 193,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-82,31; 119,21</t>
+          <t>-83,74; 111,36</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 10,81</t>
+          <t>-0,81; 10,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 9,21</t>
+          <t>-1,99; 9,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,53; —</t>
+          <t>-39,81; 1285,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 742,79</t>
+          <t>-51,09; 768,89</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 9,32</t>
+          <t>-11,47; 9,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 10,91</t>
+          <t>-7,15; 10,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-74,7; 191,82</t>
+          <t>-72,46; 179,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-76,07; 448,25</t>
+          <t>-75,26; 389,31</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 12,69</t>
+          <t>-5,86; 12,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 18,94</t>
+          <t>-1,38; 19,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 372,53</t>
+          <t>-57,32; 295,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 654,87</t>
+          <t>-18,06; 602,71</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 6,46</t>
+          <t>-5,87; 6,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 7,69</t>
+          <t>-4,74; 8,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-44,3; 103,55</t>
+          <t>-49,06; 86,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 107,83</t>
+          <t>-35,97; 125,03</t>
         </is>
       </c>
     </row>
@@ -1021,22 +1021,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 5,07</t>
+          <t>-7,26; 4,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 3,82</t>
+          <t>-5,87; 3,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,7; 58,42</t>
+          <t>-49,94; 48,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,86; 59,27</t>
+          <t>-49,11; 51,01</t>
         </is>
       </c>
     </row>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,02</t>
+          <t>-1,08; 3,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,37</t>
+          <t>-1,27; 3,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 52,58</t>
+          <t>-10,63; 52,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 50,74</t>
+          <t>-14,68; 54,23</t>
         </is>
       </c>
     </row>
